--- a/data/trans_dic/P36$pan-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36$pan-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ...</t>
+          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>71,35; 79,41</t>
+          <t>71,52; 79,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72,92; 81,38</t>
+          <t>73,44; 81,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,82; 92,77</t>
+          <t>86,37; 92,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67,49; 77,52</t>
+          <t>67,65; 77,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,54; 86,3</t>
+          <t>76,97; 86,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,29; 93,46</t>
+          <t>87,09; 93,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,53; 77,4</t>
+          <t>71,61; 78,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>76,14; 82,6</t>
+          <t>76,54; 82,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>88,01; 92,28</t>
+          <t>88,1; 92,25</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>69,83; 79,34</t>
+          <t>70,08; 79,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80,29; 88,2</t>
+          <t>80,06; 88,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,05; 90,43</t>
+          <t>83,04; 90,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70,84; 79,49</t>
+          <t>70,11; 79,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>76,6; 85,41</t>
+          <t>75,83; 85,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,68; 90,71</t>
+          <t>83,25; 90,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,72; 78,04</t>
+          <t>71,58; 78,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>80,14; 85,91</t>
+          <t>80,04; 85,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>84,24; 89,64</t>
+          <t>84,52; 89,48</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68,12; 76,39</t>
+          <t>68,09; 76,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,36; 84,07</t>
+          <t>77,17; 84,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,46; 88,82</t>
+          <t>82,36; 88,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68,48; 81,49</t>
+          <t>67,99; 81,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>78,4; 88,03</t>
+          <t>78,62; 87,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,78; 90,4</t>
+          <t>79,83; 90,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,79; 76,85</t>
+          <t>69,51; 76,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>78,82; 84,25</t>
+          <t>79,19; 84,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82,79; 88,29</t>
+          <t>82,64; 88,26</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,18; 79,95</t>
+          <t>75,21; 79,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77,05; 81,88</t>
+          <t>77,21; 82,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,23; 84,58</t>
+          <t>80,44; 84,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,27; 80,21</t>
+          <t>74,19; 80,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,54; 85,52</t>
+          <t>80,06; 85,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,33; 88,09</t>
+          <t>83,08; 88,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,5; 79,39</t>
+          <t>75,32; 79,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>78,96; 82,76</t>
+          <t>79,13; 82,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>82,22; 85,49</t>
+          <t>82,2; 85,56</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,72; 80,73</t>
+          <t>71,53; 80,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>72,99; 80,58</t>
+          <t>73,0; 80,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77,02; 83,62</t>
+          <t>76,53; 83,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76,13; 83,07</t>
+          <t>76,17; 83,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>79,37; 85,17</t>
+          <t>79,77; 85,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,39; 88,52</t>
+          <t>83,51; 88,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,84; 81,2</t>
+          <t>75,72; 81,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>78,14; 82,57</t>
+          <t>77,95; 82,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>81,32; 85,49</t>
+          <t>81,21; 85,47</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>77,14; 85,93</t>
+          <t>77,36; 85,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>77,77; 87,23</t>
+          <t>77,67; 87,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>82,77; 90,83</t>
+          <t>83,19; 91,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>78,12; 82,64</t>
+          <t>78,02; 82,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>81,87; 86,08</t>
+          <t>81,77; 86,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>87,63; 91,42</t>
+          <t>87,64; 91,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>78,54; 82,65</t>
+          <t>78,51; 82,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>81,5; 85,47</t>
+          <t>81,6; 85,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87,51; 91,02</t>
+          <t>87,34; 90,8</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>74,81; 77,91</t>
+          <t>74,86; 77,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>78,64; 81,44</t>
+          <t>78,53; 81,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83,24; 85,79</t>
+          <t>83,12; 85,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76,61; 79,45</t>
+          <t>76,62; 79,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,64; 84,17</t>
+          <t>81,48; 84,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,52; 88,7</t>
+          <t>86,57; 88,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,32; 78,4</t>
+          <t>76,37; 78,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>80,61; 82,54</t>
+          <t>80,65; 82,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>85,29; 87,0</t>
+          <t>85,34; 87,02</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ...</t>
+          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>337397; 375507</t>
+          <t>338184; 374401</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>318828; 355823</t>
+          <t>321109; 356950</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>372529; 398049</t>
+          <t>370591; 397222</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>206970; 237742</t>
+          <t>207455; 238525</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>239783; 270362</t>
+          <t>241153; 271247</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>302937; 324361</t>
+          <t>302266; 324062</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>557597; 603402</t>
+          <t>558239; 608182</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>571433; 619953</t>
+          <t>574401; 620064</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>683098; 716194</t>
+          <t>683806; 715978</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>254993; 289726</t>
+          <t>255889; 289281</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>334630; 367574</t>
+          <t>333677; 367608</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>313280; 341140</t>
+          <t>313231; 340671</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>262667; 294760</t>
+          <t>259962; 295207</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>258930; 288697</t>
+          <t>256316; 287698</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>310603; 336698</t>
+          <t>308980; 335036</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>527814; 574370</t>
+          <t>526823; 574277</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>604901; 648443</t>
+          <t>604091; 646750</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>630472; 670858</t>
+          <t>632547; 669627</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>368078; 412813</t>
+          <t>367952; 412197</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>485472; 527598</t>
+          <t>484258; 527832</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>429444; 462596</t>
+          <t>428958; 460495</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>114896; 136727</t>
+          <t>114068; 137088</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>203937; 228981</t>
+          <t>204520; 228787</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>132525; 150173</t>
+          <t>132623; 150122</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>494196; 544183</t>
+          <t>492258; 540753</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>699703; 747834</t>
+          <t>702973; 747873</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>568728; 606469</t>
+          <t>567675; 606322</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>929465; 988448</t>
+          <t>929830; 988002</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>892224; 948109</t>
+          <t>893982; 949944</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>921502; 971443</t>
+          <t>923906; 973396</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>529773; 572114</t>
+          <t>529183; 572880</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>608246; 653976</t>
+          <t>612163; 653061</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>688208; 727494</t>
+          <t>686109; 728842</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1471929; 1547864</t>
+          <t>1468495; 1545501</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1518024; 1591064</t>
+          <t>1521263; 1589593</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1623429; 1688023</t>
+          <t>1623046; 1689395</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>251432; 282986</t>
+          <t>250749; 281818</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>372011; 410723</t>
+          <t>372070; 410309</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>476700; 517552</t>
+          <t>473635; 516157</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>431514; 470802</t>
+          <t>431742; 470491</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>602037; 646081</t>
+          <t>605129; 646759</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>615601; 653519</t>
+          <t>616534; 653756</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>695705; 744901</t>
+          <t>694641; 746475</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>991057; 1047141</t>
+          <t>988624; 1045758</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1103651; 1160223</t>
+          <t>1102212; 1159909</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>230032; 256257</t>
+          <t>230677; 256327</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>207562; 232811</t>
+          <t>207296; 232589</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>237660; 260820</t>
+          <t>238875; 261453</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>975504; 1031950</t>
+          <t>974258; 1029669</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>908189; 954968</t>
+          <t>907090; 956536</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>946277; 987222</t>
+          <t>946442; 987763</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1214972; 1278513</t>
+          <t>1214529; 1277674</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1121563; 1176316</t>
+          <t>1122995; 1178126</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1196250; 1244227</t>
+          <t>1193963; 1241288</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2441296; 2542407</t>
+          <t>2443162; 2545276</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2686353; 2782138</t>
+          <t>2682440; 2780350</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2815125; 2901295</t>
+          <t>2811075; 2898268</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2584799; 2680561</t>
+          <t>2585396; 2680864</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2893412; 2983149</t>
+          <t>2887542; 2986124</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3052809; 3129669</t>
+          <t>3054404; 3134699</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5065886; 5204039</t>
+          <t>5068938; 5201020</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5610706; 5744668</t>
+          <t>5613415; 5744546</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5893773; 6011714</t>
+          <t>5897015; 6013108</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$pan-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36$pan-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>71,52; 79,18</t>
+          <t>71,46; 79,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,44; 81,64</t>
+          <t>73,58; 81,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,37; 92,57</t>
+          <t>86,72; 92,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67,65; 77,78</t>
+          <t>67,46; 77,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,97; 86,58</t>
+          <t>76,51; 86,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,09; 93,37</t>
+          <t>86,74; 93,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,61; 78,02</t>
+          <t>71,51; 77,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>76,54; 82,62</t>
+          <t>76,27; 82,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>88,1; 92,25</t>
+          <t>87,82; 92,22</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>70,08; 79,22</t>
+          <t>70,27; 79,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80,06; 88,2</t>
+          <t>80,7; 87,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,04; 90,31</t>
+          <t>83,28; 90,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70,11; 79,62</t>
+          <t>70,51; 79,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>75,83; 85,11</t>
+          <t>76,16; 85,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,25; 90,27</t>
+          <t>83,32; 90,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,58; 78,03</t>
+          <t>71,42; 77,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>80,04; 85,69</t>
+          <t>79,93; 85,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>84,52; 89,48</t>
+          <t>84,58; 89,58</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68,09; 76,28</t>
+          <t>68,83; 76,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,17; 84,11</t>
+          <t>77,37; 84,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,36; 88,42</t>
+          <t>82,29; 88,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67,99; 81,71</t>
+          <t>68,51; 81,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>78,62; 87,95</t>
+          <t>78,85; 88,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,83; 90,37</t>
+          <t>79,96; 90,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,51; 76,36</t>
+          <t>69,43; 76,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>79,19; 84,25</t>
+          <t>78,67; 84,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82,64; 88,26</t>
+          <t>82,5; 88,22</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,21; 79,92</t>
+          <t>74,98; 79,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77,21; 82,04</t>
+          <t>77,32; 82,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,44; 84,75</t>
+          <t>80,53; 84,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,19; 80,31</t>
+          <t>73,86; 80,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,06; 85,4</t>
+          <t>79,81; 85,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,08; 88,25</t>
+          <t>82,77; 87,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,32; 79,27</t>
+          <t>75,74; 79,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>79,13; 82,68</t>
+          <t>78,88; 82,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>82,2; 85,56</t>
+          <t>82,19; 85,62</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,53; 80,39</t>
+          <t>71,16; 80,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73,0; 80,5</t>
+          <t>73,06; 80,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76,53; 83,4</t>
+          <t>76,78; 83,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76,17; 83,01</t>
+          <t>76,54; 83,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>79,77; 85,26</t>
+          <t>79,62; 85,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,51; 88,56</t>
+          <t>83,38; 88,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,72; 81,37</t>
+          <t>75,8; 81,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>77,95; 82,46</t>
+          <t>77,95; 82,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>81,21; 85,47</t>
+          <t>81,49; 85,46</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>77,36; 85,96</t>
+          <t>77,01; 85,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>77,67; 87,15</t>
+          <t>77,82; 86,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83,19; 91,05</t>
+          <t>82,93; 90,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>78,02; 82,46</t>
+          <t>77,91; 82,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>81,77; 86,22</t>
+          <t>81,55; 86,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>87,64; 91,47</t>
+          <t>87,68; 91,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>78,51; 82,59</t>
+          <t>78,51; 82,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>81,6; 85,61</t>
+          <t>81,68; 85,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87,34; 90,8</t>
+          <t>87,43; 90,84</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>74,86; 77,99</t>
+          <t>75,03; 77,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>78,53; 81,39</t>
+          <t>78,63; 81,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83,12; 85,7</t>
+          <t>83,11; 85,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76,62; 79,45</t>
+          <t>76,51; 79,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,48; 84,26</t>
+          <t>81,7; 84,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,57; 88,84</t>
+          <t>86,52; 88,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,37; 78,36</t>
+          <t>76,33; 78,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>80,65; 82,54</t>
+          <t>80,68; 82,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>85,34; 87,02</t>
+          <t>85,25; 86,95</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>338184; 374401</t>
+          <t>337913; 376517</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>321109; 356950</t>
+          <t>321693; 358398</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>370591; 397222</t>
+          <t>372119; 397510</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>207455; 238525</t>
+          <t>206877; 237427</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>241153; 271247</t>
+          <t>239689; 270474</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>302266; 324062</t>
+          <t>301023; 324321</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>558239; 608182</t>
+          <t>557472; 606289</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>574401; 620064</t>
+          <t>572390; 619136</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>683806; 715978</t>
+          <t>681608; 715761</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>255889; 289281</t>
+          <t>256597; 289576</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>333677; 367608</t>
+          <t>336321; 366559</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>313231; 340671</t>
+          <t>314144; 341357</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>259962; 295207</t>
+          <t>261443; 294876</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>256316; 287698</t>
+          <t>257445; 287961</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>308980; 335036</t>
+          <t>309256; 337438</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>526823; 574277</t>
+          <t>525603; 573903</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>604091; 646750</t>
+          <t>603294; 648374</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>632547; 669627</t>
+          <t>632997; 670418</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>367952; 412197</t>
+          <t>371949; 412151</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>484258; 527832</t>
+          <t>485513; 527569</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>428958; 460495</t>
+          <t>428585; 460601</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>114068; 137088</t>
+          <t>114950; 136534</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>204520; 228787</t>
+          <t>205121; 229303</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>132623; 150122</t>
+          <t>132837; 151032</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>492258; 540753</t>
+          <t>491645; 539563</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>702973; 747873</t>
+          <t>698330; 749297</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>567675; 606322</t>
+          <t>566703; 606035</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>929830; 988002</t>
+          <t>926909; 986536</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>893982; 949944</t>
+          <t>895263; 950327</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>923906; 973396</t>
+          <t>924964; 975276</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>529183; 572880</t>
+          <t>526853; 572941</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>612163; 653061</t>
+          <t>610291; 653916</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>686109; 728842</t>
+          <t>683546; 726528</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1468495; 1545501</t>
+          <t>1476544; 1545574</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1521263; 1589593</t>
+          <t>1516453; 1590143</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1623046; 1689395</t>
+          <t>1622715; 1690525</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>250749; 281818</t>
+          <t>249448; 282734</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>372070; 410309</t>
+          <t>372363; 409615</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473635; 516157</t>
+          <t>475225; 514388</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>431742; 470491</t>
+          <t>433821; 471201</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>605129; 646759</t>
+          <t>603983; 646468</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>616534; 653756</t>
+          <t>615516; 653072</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>694641; 746475</t>
+          <t>695324; 746960</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>988624; 1045758</t>
+          <t>988610; 1047298</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1102212; 1159909</t>
+          <t>1105919; 1159794</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>230677; 256327</t>
+          <t>229649; 255107</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>207296; 232589</t>
+          <t>207700; 232052</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>238875; 261453</t>
+          <t>238131; 260764</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>974258; 1029669</t>
+          <t>972852; 1031725</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>907090; 956536</t>
+          <t>904670; 954020</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>946442; 987763</t>
+          <t>946838; 988178</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1214529; 1277674</t>
+          <t>1214505; 1278214</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1122995; 1178126</t>
+          <t>1124087; 1178420</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1193963; 1241288</t>
+          <t>1195203; 1241870</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2443162; 2545276</t>
+          <t>2448706; 2541134</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2682440; 2780350</t>
+          <t>2686010; 2787490</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2811075; 2898268</t>
+          <t>2810710; 2898192</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2585396; 2680864</t>
+          <t>2581544; 2682068</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2887542; 2986124</t>
+          <t>2895567; 2983949</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3054404; 3134699</t>
+          <t>3052613; 3134773</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5068938; 5201020</t>
+          <t>5066606; 5200319</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5613415; 5744546</t>
+          <t>5615214; 5744365</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5897015; 6013108</t>
+          <t>5890854; 6008536</t>
         </is>
       </c>
     </row>
